--- a/r4-core-153-healthcareservice-profile/StructureDefinition-at-core-location.xlsx
+++ b/r4-core-153-healthcareservice-profile/StructureDefinition-at-core-location.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="385">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T21:21:27+00:00</t>
+    <t>2026-10-11T19:39:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -963,6 +963,10 @@
   </si>
   <si>
     <t>If locations can be visited, we need to keep track of their address.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+at-addr-1:If the extension for street name is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-streetName').empty() or $this.hasValue())}at-addr-2:If the extension for street number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-houseNumber').empty() or $this.hasValue())}at-addr-3:If the extension for floor/door number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-additionalLocator').empty() or $this.hasValue())}</t>
   </si>
   <si>
     <t>.addr</t>
@@ -5333,10 +5337,10 @@
         <v>21</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>96</v>
+        <v>306</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>21</v>
@@ -5344,10 +5348,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5373,14 +5377,14 @@
         <v>179</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -5405,13 +5409,13 @@
         <v>21</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>21</v>
@@ -5429,7 +5433,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5444,7 +5448,7 @@
         <v>96</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>289</v>
@@ -5452,10 +5456,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5478,17 +5482,17 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -5537,7 +5541,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5552,7 +5556,7 @@
         <v>96</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
@@ -5560,10 +5564,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5666,10 +5670,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5774,14 +5778,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5803,10 +5807,10 @@
         <v>130</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>133</v>
@@ -5861,7 +5865,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5884,10 +5888,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5910,13 +5914,13 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5967,7 +5971,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>84</v>
@@ -5982,7 +5986,7 @@
         <v>96</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
@@ -5990,10 +5994,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6016,13 +6020,13 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6073,7 +6077,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>84</v>
@@ -6088,7 +6092,7 @@
         <v>96</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
@@ -6096,10 +6100,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6122,13 +6126,13 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6179,7 +6183,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6194,7 +6198,7 @@
         <v>96</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>21</v>
@@ -6202,10 +6206,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6228,19 +6232,19 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -6289,7 +6293,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6304,7 +6308,7 @@
         <v>96</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
@@ -6312,10 +6316,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6338,17 +6342,17 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -6397,7 +6401,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6412,7 +6416,7 @@
         <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
@@ -6420,10 +6424,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6446,16 +6450,16 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6505,7 +6509,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6520,7 +6524,7 @@
         <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>21</v>
@@ -6528,10 +6532,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6634,10 +6638,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6742,14 +6746,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6771,10 +6775,10 @@
         <v>130</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>133</v>
@@ -6829,7 +6833,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6852,10 +6856,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6881,10 +6885,10 @@
         <v>104</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6914,10 +6918,10 @@
         <v>172</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>21</v>
@@ -6935,7 +6939,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -6950,7 +6954,7 @@
         <v>96</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
@@ -6958,10 +6962,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6984,13 +6988,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7041,7 +7045,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7056,7 +7060,7 @@
         <v>96</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>21</v>
@@ -7064,10 +7068,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7090,13 +7094,13 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7147,7 +7151,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7162,7 +7166,7 @@
         <v>96</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
@@ -7170,10 +7174,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7196,13 +7200,13 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7253,7 +7257,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7268,7 +7272,7 @@
         <v>96</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>21</v>
@@ -7276,10 +7280,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7305,10 +7309,10 @@
         <v>155</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7359,7 +7363,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7382,10 +7386,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7408,17 +7412,17 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -7467,7 +7471,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>

--- a/r4-core-153-healthcareservice-profile/StructureDefinition-at-core-location.xlsx
+++ b/r4-core-153-healthcareservice-profile/StructureDefinition-at-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-11T19:39:36+00:00</t>
+    <t>2026-10-12T11:53:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
